--- a/data/trans_orig/P19D-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19D-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de dentista que consultó en 2007</t>
+          <t>Población según a dónde pertenecía el último dentista al que consultó en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6035</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1953</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6714</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6485</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7041</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>425670</t>
+          <t>425612</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>450259</t>
+          <t>449457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>491062</t>
+          <t>489744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>512477</t>
+          <t>512865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>923936</t>
+          <t>920838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>958555</t>
+          <t>956781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21986</t>
+          <t>22282</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44728</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18922</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39511</t>
+          <t>39428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>46210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76097</t>
+          <t>79155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -1302,82 +1302,82 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2073</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>1528</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>7622</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1528</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>641383</t>
+          <t>641678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>671328</t>
+          <t>673184</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>719428</t>
+          <t>717677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>751562</t>
+          <t>751333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1370628</t>
+          <t>1371749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1417454</t>
+          <t>1416321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24329</t>
+          <t>24254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>23108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42706</t>
+          <t>41419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>35960</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62798</t>
+          <t>64436</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68120</t>
+          <t>68041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82136</t>
+          <t>82344</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122931</t>
+          <t>121086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -1871,82 +1871,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5367</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1074</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5398</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>471780</t>
+          <t>469213</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>500306</t>
+          <t>500200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>514872</t>
+          <t>516218</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>541945</t>
+          <t>543403</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>996237</t>
+          <t>995634</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1035714</t>
+          <t>1038618</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24494</t>
+          <t>24111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36374</t>
+          <t>36819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35145</t>
+          <t>35861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>65875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28323</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50952</t>
+          <t>50288</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70026</t>
+          <t>69031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105477</t>
+          <t>105648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>620749</t>
+          <t>621483</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>653092</t>
+          <t>651546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>712894</t>
+          <t>710747</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>747451</t>
+          <t>747277</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1343543</t>
+          <t>1342935</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1391772</t>
+          <t>1391947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35157</t>
+          <t>34766</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25633</t>
+          <t>25320</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>28040</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>53645</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61874</t>
+          <t>61831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49486</t>
+          <t>50808</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81404</t>
+          <t>82835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93647</t>
+          <t>94415</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133245</t>
+          <t>137193</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2191445</t>
+          <t>2190757</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2253268</t>
+          <t>2249704</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2471115</t>
+          <t>2467496</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2531552</t>
+          <t>2527200</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4680531</t>
+          <t>4677526</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4763510</t>
+          <t>4758395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72124</t>
+          <t>73089</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37845</t>
+          <t>37393</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67775</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>88227</t>
+          <t>85682</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>129118</t>
+          <t>127078</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>148770</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>203077</t>
+          <t>203230</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>158520</t>
+          <t>159488</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>211288</t>
+          <t>211701</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>325731</t>
+          <t>327531</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>399121</t>
+          <t>397914</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de dentista que consultó en 2012</t>
+          <t>Población según a dónde pertenecía el último dentista al que consultó en 2012 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,97 +3810,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478106</t>
+          <t>478838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>517727</t>
+          <t>518187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>528344</t>
+          <t>528869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>564137</t>
+          <t>565189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1019420</t>
+          <t>1021556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1070223</t>
+          <t>1072645</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>22269</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34393</t>
+          <t>34699</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75430</t>
+          <t>74543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111252</t>
+          <t>111358</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61548</t>
+          <t>60243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95752</t>
+          <t>96430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145658</t>
+          <t>145688</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195395</t>
+          <t>195522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -4379,97 +4379,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2081</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>687700</t>
+          <t>689179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>735881</t>
+          <t>735078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>756358</t>
+          <t>756874</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>798323</t>
+          <t>798165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1458686</t>
+          <t>1460945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1523681</t>
+          <t>1525679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>14140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36296</t>
+          <t>37901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55101</t>
+          <t>54917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106995</t>
+          <t>107753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151510</t>
+          <t>150640</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90679</t>
+          <t>89769</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129699</t>
+          <t>128258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>207582</t>
+          <t>207040</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>266091</t>
+          <t>265669</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,62 +4983,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>8344</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>8003</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>489124</t>
+          <t>488287</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>530983</t>
+          <t>531715</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>570207</t>
+          <t>568316</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>607575</t>
+          <t>606600</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1066827</t>
+          <t>1071363</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1125171</t>
+          <t>1126948</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>18910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43681</t>
+          <t>43894</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37102</t>
+          <t>36139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37770</t>
+          <t>37463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70480</t>
+          <t>71001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74806</t>
+          <t>73514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110984</t>
+          <t>111633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52914</t>
+          <t>54188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84465</t>
+          <t>87729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138654</t>
+          <t>136846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188580</t>
+          <t>187562</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -5517,97 +5517,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>666757</t>
+          <t>666360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>707030</t>
+          <t>706673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>780194</t>
+          <t>779348</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>822480</t>
+          <t>823089</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1459039</t>
+          <t>1457557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1518737</t>
+          <t>1519460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>46261</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>24179</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48505</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>50785</t>
+          <t>51307</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83895</t>
+          <t>85998</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67452</t>
+          <t>67853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101711</t>
+          <t>104518</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73880</t>
+          <t>73611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112536</t>
+          <t>110341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>150706</t>
+          <t>152377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>203309</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,47 +6121,47 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2073</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2371742</t>
+          <t>2367256</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2453470</t>
+          <t>2452360</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2676021</t>
+          <t>2680512</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2756884</t>
+          <t>2754528</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5077063</t>
+          <t>5076828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5193922</t>
+          <t>5189607</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78259</t>
+          <t>76737</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121921</t>
+          <t>121059</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63509</t>
+          <t>62788</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>102492</t>
+          <t>102527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152399</t>
+          <t>152332</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>209368</t>
+          <t>211706</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>359894</t>
+          <t>355589</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>434507</t>
+          <t>432742</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>309159</t>
+          <t>310960</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>381944</t>
+          <t>381103</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>687640</t>
+          <t>685550</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>793264</t>
+          <t>790818</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de dentista que consultó en 2016</t>
+          <t>Población según a dónde pertenecía el último dentista al que consultó en 2016 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,97 +6887,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449627</t>
+          <t>450345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>480165</t>
+          <t>479789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>478161</t>
+          <t>477654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>504726</t>
+          <t>506455</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>937749</t>
+          <t>936581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>977159</t>
+          <t>977192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>42692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71641</t>
+          <t>71527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>34027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62508</t>
+          <t>62039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86079</t>
+          <t>85652</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124872</t>
+          <t>125367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>706233</t>
+          <t>707419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>744635</t>
+          <t>743979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>752940</t>
+          <t>754496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>791147</t>
+          <t>790011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1473368</t>
+          <t>1473021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1524202</t>
+          <t>1525754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31511</t>
+          <t>31913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26446</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,47 +7732,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>36752</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>25042</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>51349</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>3,05%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>36752</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>24308</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>50522</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51893</t>
+          <t>52552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86091</t>
+          <t>84382</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58274</t>
+          <t>58926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93650</t>
+          <t>91112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>119304</t>
+          <t>119785</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>167619</t>
+          <t>166695</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -8025,97 +8025,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>481582</t>
+          <t>480084</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>509186</t>
+          <t>509766</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>499577</t>
+          <t>501345</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>531141</t>
+          <t>530174</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>989821</t>
+          <t>990297</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1033951</t>
+          <t>1031493</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29206</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61248</t>
+          <t>63136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58159</t>
+          <t>56851</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>72431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112668</t>
+          <t>110187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,62 +8629,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4566</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4967</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>650843</t>
+          <t>649390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>688744</t>
+          <t>687676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>713810</t>
+          <t>714235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>758204</t>
+          <t>760652</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1381052</t>
+          <t>1380134</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1440575</t>
+          <t>1438576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>35912</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>36066</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65895</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>56982</t>
+          <t>55844</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92311</t>
+          <t>92804</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60902</t>
+          <t>59185</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92105</t>
+          <t>93580</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71942</t>
+          <t>71957</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109358</t>
+          <t>108609</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>142290</t>
+          <t>142617</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>189116</t>
+          <t>192635</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2325712</t>
+          <t>2325613</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2395217</t>
+          <t>2391673</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2488761</t>
+          <t>2488411</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2554473</t>
+          <t>2562663</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4828008</t>
+          <t>4838868</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4933078</t>
+          <t>4934106</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68958</t>
+          <t>68222</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70539</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109454</t>
+          <t>106151</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>116322</t>
+          <t>118136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>169139</t>
+          <t>166348</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>216610</t>
+          <t>216888</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>280109</t>
+          <t>279167</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>226084</t>
+          <t>224481</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>287617</t>
+          <t>284889</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>459507</t>
+          <t>458366</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>548338</t>
+          <t>538181</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de dentista que consultó en 2023</t>
+          <t>Población según a dónde pertenecía el último dentista al que consultó en 2023 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,97 +9964,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1685</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1282</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>535378</t>
+          <t>534190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>568934</t>
+          <t>569823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>601989</t>
+          <t>601699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>619982</t>
+          <t>619240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1145226</t>
+          <t>1141441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1182889</t>
+          <t>1182290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42694</t>
+          <t>42298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75662</t>
+          <t>76943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26669</t>
+          <t>26535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43024</t>
+          <t>43371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>75231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111348</t>
+          <t>114505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -10533,97 +10533,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2391</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1671</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>454047</t>
+          <t>450702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1063738</t>
+          <t>1064013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>870113</t>
+          <t>869790</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>895563</t>
+          <t>896662</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1175420</t>
+          <t>1191045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1949571</t>
+          <t>1950339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>30575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36030</t>
+          <t>36189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85642</t>
+          <t>83715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704018</t>
+          <t>703519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43472</t>
+          <t>41879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66575</t>
+          <t>67943</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>137552</t>
+          <t>138456</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>924380</t>
+          <t>912564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -11102,97 +11102,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>594915</t>
+          <t>595021</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>635834</t>
+          <t>634604</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>856828</t>
+          <t>856406</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>901451</t>
+          <t>902161</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1464085</t>
+          <t>1464939</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1538133</t>
+          <t>1537175</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26966</t>
+          <t>26556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16636</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43943</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74357</t>
+          <t>73688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50490</t>
+          <t>51308</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54960</t>
+          <t>55966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113696</t>
+          <t>115207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -11671,97 +11671,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1771</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>768373</t>
+          <t>768677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>810625</t>
+          <t>810710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>956903</t>
+          <t>957743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>997793</t>
+          <t>999212</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1741400</t>
+          <t>1737787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1801260</t>
+          <t>1799843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33454</t>
+          <t>34153</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>23910</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48856</t>
+          <t>48603</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55957</t>
+          <t>55798</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96209</t>
+          <t>96427</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53121</t>
+          <t>52591</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90576</t>
+          <t>90566</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114698</t>
+          <t>116446</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171055</t>
+          <t>172800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -12240,97 +12240,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1572</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2156026</t>
+          <t>2076520</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3030794</t>
+          <t>3031926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3321010</t>
+          <t>3318958</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3393184</t>
+          <t>3395953</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5476319</t>
+          <t>5359313</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6400010</t>
+          <t>6399589</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37647</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74388</t>
+          <t>75183</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28844</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52601</t>
+          <t>52843</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>73260</t>
+          <t>73369</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>117726</t>
+          <t>117209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>263617</t>
+          <t>264103</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1160014</t>
+          <t>1231091</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154165</t>
+          <t>153103</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>219809</t>
+          <t>222707</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>442400</t>
+          <t>441272</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1366055</t>
+          <t>1491175</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19D-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19D-Habitat-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>425612</t>
+          <t>424756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449457</t>
+          <t>449885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>489744</t>
+          <t>489451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>512865</t>
+          <t>512696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>920838</t>
+          <t>924162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>956781</t>
+          <t>956937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44166</t>
+          <t>45505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18857</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39428</t>
+          <t>40165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>47157</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79155</t>
+          <t>77525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>641678</t>
+          <t>643136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>673184</t>
+          <t>672128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>717677</t>
+          <t>718562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>751333</t>
+          <t>751046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1371749</t>
+          <t>1370593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1416321</t>
+          <t>1415184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>24458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19226</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41419</t>
+          <t>41023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35960</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64436</t>
+          <t>61463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>40158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68041</t>
+          <t>68936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82344</t>
+          <t>82170</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121086</t>
+          <t>123264</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>469213</t>
+          <t>472724</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>500200</t>
+          <t>501003</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>516218</t>
+          <t>515383</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>543403</t>
+          <t>543323</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>995634</t>
+          <t>995541</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1038618</t>
+          <t>1034719</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>24845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36819</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35861</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65875</t>
+          <t>63025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26976</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50288</t>
+          <t>50805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>71095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105648</t>
+          <t>105913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -2440,97 +2440,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>7129</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2242</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>7601</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>4877</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1772</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>11804</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2242</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7905</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>4877</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1751</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11102</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>621483</t>
+          <t>620624</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>651546</t>
+          <t>651694</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>710747</t>
+          <t>710757</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>747277</t>
+          <t>745293</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1342935</t>
+          <t>1344556</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1391947</t>
+          <t>1390244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>15823</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>34867</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25320</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>53419</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36359</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61831</t>
+          <t>62764</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50808</t>
+          <t>51406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82835</t>
+          <t>81569</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94415</t>
+          <t>94268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137193</t>
+          <t>134468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,47 +3059,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>9431</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>4793</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>18052</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>9431</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>16988</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2190757</t>
+          <t>2192652</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2249704</t>
+          <t>2250311</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2467496</t>
+          <t>2467197</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2527200</t>
+          <t>2525577</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4677526</t>
+          <t>4677792</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4758395</t>
+          <t>4762543</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>42953</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73089</t>
+          <t>73623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>38099</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66076</t>
+          <t>66273</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>85682</t>
+          <t>83012</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127078</t>
+          <t>126249</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>151457</t>
+          <t>154159</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>203230</t>
+          <t>204118</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>159488</t>
+          <t>159527</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>211701</t>
+          <t>212697</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>327531</t>
+          <t>323118</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>397914</t>
+          <t>399839</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478838</t>
+          <t>478971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>518187</t>
+          <t>519302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>528869</t>
+          <t>526628</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>565189</t>
+          <t>564392</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1021556</t>
+          <t>1015914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1072645</t>
+          <t>1071399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>22255</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34699</t>
+          <t>33274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74543</t>
+          <t>74339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111358</t>
+          <t>111990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60243</t>
+          <t>59186</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96430</t>
+          <t>95564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145688</t>
+          <t>145976</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195522</t>
+          <t>197928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>689179</t>
+          <t>689824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>735078</t>
+          <t>737562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>756874</t>
+          <t>756628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>798165</t>
+          <t>798498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1460945</t>
+          <t>1461130</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1525679</t>
+          <t>1524101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37901</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22498</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>26214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54917</t>
+          <t>53998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107753</t>
+          <t>105137</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>150640</t>
+          <t>148812</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89769</t>
+          <t>89460</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>128258</t>
+          <t>131150</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>207040</t>
+          <t>206589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>265669</t>
+          <t>263758</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>488287</t>
+          <t>487720</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>531715</t>
+          <t>530142</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,82 +5076,82 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>83,48%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>589088</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>568838</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>607480</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>89,41%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>1100671</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>1072170</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>1131442</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
           <t>83,73%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>589088</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>568316</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>606600</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>83,65%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>89,28%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1100671</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1071363</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1126948</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43894</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36139</t>
+          <t>35607</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37463</t>
+          <t>37364</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71001</t>
+          <t>70419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73514</t>
+          <t>75885</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111633</t>
+          <t>112324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54188</t>
+          <t>52764</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87729</t>
+          <t>85745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136846</t>
+          <t>133288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>187562</t>
+          <t>185233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>666360</t>
+          <t>666383</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>706673</t>
+          <t>708940</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>779348</t>
+          <t>780908</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>823089</t>
+          <t>824236</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1457557</t>
+          <t>1459638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1519460</t>
+          <t>1520116</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46261</t>
+          <t>45658</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>47334</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>51307</t>
+          <t>50503</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>85998</t>
+          <t>83709</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67853</t>
+          <t>66128</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104518</t>
+          <t>101341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73611</t>
+          <t>74177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110341</t>
+          <t>111997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>152377</t>
+          <t>149414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>203309</t>
+          <t>200685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2367256</t>
+          <t>2368691</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2452360</t>
+          <t>2452523</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2680512</t>
+          <t>2677543</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2754528</t>
+          <t>2753063</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5076828</t>
+          <t>5066403</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5189607</t>
+          <t>5189476</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76737</t>
+          <t>77277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121059</t>
+          <t>117552</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62788</t>
+          <t>63744</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>102527</t>
+          <t>104125</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152332</t>
+          <t>152464</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>211706</t>
+          <t>212135</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>355589</t>
+          <t>358780</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>432742</t>
+          <t>437270</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>310960</t>
+          <t>312089</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>381103</t>
+          <t>383088</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>685550</t>
+          <t>688484</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>790818</t>
+          <t>796289</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450345</t>
+          <t>451108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>479789</t>
+          <t>480921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>477654</t>
+          <t>479161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>506455</t>
+          <t>505523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>936581</t>
+          <t>937401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>977192</t>
+          <t>977882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42692</t>
+          <t>42709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71527</t>
+          <t>71405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34027</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62039</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85652</t>
+          <t>84959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125367</t>
+          <t>124563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>707419</t>
+          <t>705820</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>743979</t>
+          <t>744046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>754496</t>
+          <t>752456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>790011</t>
+          <t>790779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1473021</t>
+          <t>1475025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1525754</t>
+          <t>1529687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12308</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31913</t>
+          <t>29958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26120</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51349</t>
+          <t>51558</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52552</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84382</t>
+          <t>84471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58926</t>
+          <t>59194</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91112</t>
+          <t>93639</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>119785</t>
+          <t>118773</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>166695</t>
+          <t>165630</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>480084</t>
+          <t>478479</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>509766</t>
+          <t>508879</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>501345</t>
+          <t>499855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>530174</t>
+          <t>530727</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>990297</t>
+          <t>990931</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1031493</t>
+          <t>1030647</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8271,42 +8271,42 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>18989</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11172</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29493</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>18989</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11771</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30451</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>35926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>35176</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63136</t>
+          <t>64891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56851</t>
+          <t>55922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72431</t>
+          <t>74424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110187</t>
+          <t>111087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>649390</t>
+          <t>649989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>687676</t>
+          <t>687989</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>714235</t>
+          <t>713854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>760652</t>
+          <t>759816</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1380134</t>
+          <t>1376452</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1438576</t>
+          <t>1436778</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35912</t>
+          <t>36211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36066</t>
+          <t>36186</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65199</t>
+          <t>65347</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>58906</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92804</t>
+          <t>94892</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59185</t>
+          <t>60213</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93580</t>
+          <t>92509</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71957</t>
+          <t>73294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108609</t>
+          <t>110014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>142617</t>
+          <t>142334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>192635</t>
+          <t>193210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2325613</t>
+          <t>2328680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2391673</t>
+          <t>2394741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2488411</t>
+          <t>2484736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2562663</t>
+          <t>2553016</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4838868</t>
+          <t>4831643</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4934106</t>
+          <t>4928084</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39548</t>
+          <t>38055</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68222</t>
+          <t>68158</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67103</t>
+          <t>70998</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>106151</t>
+          <t>109683</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>118136</t>
+          <t>116351</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>166348</t>
+          <t>164930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>216888</t>
+          <t>216282</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>279167</t>
+          <t>275981</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>224481</t>
+          <t>224495</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>284889</t>
+          <t>283527</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>458366</t>
+          <t>459685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>538181</t>
+          <t>546080</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>555219</t>
+          <t>597342</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>534190</t>
+          <t>577282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>569823</t>
+          <t>611642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>661536</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>601699</t>
+          <t>650823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>619240</t>
+          <t>671017</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1166921</t>
+          <t>1258878</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1141441</t>
+          <t>1237777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1182290</t>
+          <t>1276999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -10185,67 +10185,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5553</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2872</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9699</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5293</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2646</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9647</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,22 +10255,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>62449</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42298</t>
+          <t>48375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76943</t>
+          <t>81723</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33894</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>49016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>90447</t>
+          <t>100839</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75231</t>
+          <t>83388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114505</t>
+          <t>121716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>614303</t>
+          <t>662549</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>614303</t>
+          <t>662549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>614303</t>
+          <t>662549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>650889</t>
+          <t>705479</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>650889</t>
+          <t>705479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>650889</t>
+          <t>705479</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1265192</t>
+          <t>1368028</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1265192</t>
+          <t>1368028</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1265192</t>
+          <t>1368028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>832588</t>
+          <t>913194</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>450702</t>
+          <t>890544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1064013</t>
+          <t>933678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>884860</t>
+          <t>980262</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>869790</t>
+          <t>963726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>896662</t>
+          <t>993478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1717448</t>
+          <t>1893456</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1191045</t>
+          <t>1867361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1950339</t>
+          <t>1917872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>32503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,22 +10789,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>26021</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36189</t>
+          <t>40333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>319194</t>
+          <t>85245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83715</t>
+          <t>67910</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703519</t>
+          <t>106458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>62546</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41879</t>
+          <t>50315</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67943</t>
+          <t>77388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>372463</t>
+          <t>147791</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138456</t>
+          <t>126733</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>912564</t>
+          <t>171575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1166612</t>
+          <t>1016115</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1166612</t>
+          <t>1016115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1166612</t>
+          <t>1016115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>946056</t>
+          <t>1051153</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>946056</t>
+          <t>1051153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>946056</t>
+          <t>1051153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2112668</t>
+          <t>2067268</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2112668</t>
+          <t>2067268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2112668</t>
+          <t>2067268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>618522</t>
+          <t>695401</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>595021</t>
+          <t>671657</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>634604</t>
+          <t>712641</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>877470</t>
+          <t>742682</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>856406</t>
+          <t>725458</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>902161</t>
+          <t>756595</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1495992</t>
+          <t>1438083</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1464939</t>
+          <t>1407859</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1537175</t>
+          <t>1459791</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15506</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26556</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>31742</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>35438</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>24032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44034</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52335</t>
+          <t>61316</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37662</t>
+          <t>45301</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73688</t>
+          <t>84257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15744</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51308</t>
+          <t>52750</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>87075</t>
+          <t>100539</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55966</t>
+          <t>80949</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115207</t>
+          <t>125886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>686364</t>
+          <t>773214</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>686364</t>
+          <t>773214</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>686364</t>
+          <t>773214</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>925616</t>
+          <t>800846</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>925616</t>
+          <t>800846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>925616</t>
+          <t>800846</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1611980</t>
+          <t>1574060</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1611980</t>
+          <t>1574060</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1611980</t>
+          <t>1574060</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>793361</t>
+          <t>838396</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>768677</t>
+          <t>817726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>810710</t>
+          <t>857494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>979556</t>
+          <t>987635</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>957743</t>
+          <t>971980</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>999212</t>
+          <t>1001025</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1772916</t>
+          <t>1826031</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1737787</t>
+          <t>1798934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1799843</t>
+          <t>1848461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22291</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34153</t>
+          <t>37827</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>34314</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48603</t>
+          <t>50942</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>71355</t>
+          <t>80170</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55798</t>
+          <t>63113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96427</t>
+          <t>99199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>68872</t>
+          <t>71129</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52591</t>
+          <t>58459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90566</t>
+          <t>85274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>140227</t>
+          <t>151300</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116446</t>
+          <t>130448</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172800</t>
+          <t>176635</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887007</t>
+          <t>943173</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887007</t>
+          <t>943173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887007</t>
+          <t>943173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1060450</t>
+          <t>1070951</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1060450</t>
+          <t>1070951</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1060450</t>
+          <t>1070951</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1947457</t>
+          <t>2014124</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1947457</t>
+          <t>2014124</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1947457</t>
+          <t>2014124</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2799690</t>
+          <t>3044333</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2076520</t>
+          <t>2998015</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3031926</t>
+          <t>3080629</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3353588</t>
+          <t>3372115</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3318958</t>
+          <t>3342441</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3395953</t>
+          <t>3397640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6153278</t>
+          <t>6416447</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5359313</t>
+          <t>6363929</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6399589</t>
+          <t>6464643</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>55159</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>45811</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75183</t>
+          <t>79164</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38648</t>
+          <t>45025</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52843</t>
+          <t>58632</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>93807</t>
+          <t>106563</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>73369</t>
+          <t>85542</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>117209</t>
+          <t>129995</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>499437</t>
+          <t>289180</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>264103</t>
+          <t>256671</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1231091</t>
+          <t>328757</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>190775</t>
+          <t>211289</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>153103</t>
+          <t>188175</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>222707</t>
+          <t>238187</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>690212</t>
+          <t>500469</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>441272</t>
+          <t>457186</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1491175</t>
+          <t>550184</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3354286</t>
+          <t>3395050</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3354286</t>
+          <t>3395050</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3354286</t>
+          <t>3395050</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3583011</t>
+          <t>3628429</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3583011</t>
+          <t>3628429</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3583011</t>
+          <t>3628429</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6937297</t>
+          <t>7023479</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6937297</t>
+          <t>7023479</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6937297</t>
+          <t>7023479</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
